--- a/data/trans_orig/IQ09_M-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_M-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio en meses que llevan sufriendo esa dolencia, enfermedad o impedimento que les haya limitado de forma continuada (más de 10 días en los últimos 12 meses)</t>
+          <t>Tiempo medio en meses que llevan sufriendo esa dolencia, enfermedad o impedimento que les haya limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 97,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +638,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,49</t>
+          <t>0,53; 3,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,17</t>
+          <t>0,0; 1,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 6,27</t>
+          <t>0,53; 5,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -761,24 +761,24 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,57</t>
+          <t>0,81; 3,68</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 4,07</t>
+          <t>0,47; 3,83</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,9</t>
+          <t>0,0; 1,86</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,97</t>
+          <t>0,0; 1,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -876,12 +876,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 9,0</t>
+          <t>0,0; 9,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,37</t>
+          <t>0,68; 3,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -891,34 +891,34 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 7,21</t>
+          <t>0,32; 7,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,64</t>
+          <t>0,54; 4,56</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,37</t>
+          <t>0,46; 2,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,0</t>
+          <t>0,69; 6,21</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 6,1</t>
+          <t>1,03; 6,36</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,09</t>
+          <t>0,0; 4,16</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,55</t>
+          <t>0,0; 3,85</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,81</t>
+          <t>0,0; 0,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 3,06</t>
+          <t>0,15; 3,06</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,92</t>
+          <t>0,37; 4,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 4,17</t>
+          <t>0,31; 4,12</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1331,14 +1331,14 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,28</t>
+          <t>0,37; 1,26</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,77</t>
+          <t>0,0; 3,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,97</t>
+          <t>0,0; 2,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,59; 6,55</t>
+          <t>0,74; 6,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1466,19 +1466,19 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,56</t>
+          <t>0,32; 2,64</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,59; 6,55</t>
+          <t>0,74; 6,56</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,43</t>
+          <t>0,46; 3,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1571,47 +1571,47 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,75</t>
+          <t>0,0; 0,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,12</t>
+          <t>0,51; 5,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 6,1</t>
+          <t>1,1; 6,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,97; 7,0</t>
+          <t>0,0; 7,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,83</t>
+          <t>0,15; 1,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,12</t>
+          <t>0,51; 5,07</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,87</t>
+          <t>1,03; 3,88</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,58; 5,39</t>
+          <t>0,79; 5,5</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,39</t>
+          <t>0,16; 1,49</t>
         </is>
       </c>
     </row>
@@ -1696,12 +1696,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,33</t>
+          <t>0,0; 4,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,18</t>
+          <t>0,0; 2,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1711,47 +1711,47 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,76</t>
+          <t>0,36; 1,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,76</t>
+          <t>0,0; 2,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,66</t>
+          <t>0,92; 2,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,44</t>
+          <t>0,5; 4,35</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,0</t>
+          <t>0,0; 4,98</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,46</t>
+          <t>0,24; 2,56</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,05</t>
+          <t>0,69; 2,1</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,81</t>
+          <t>0,85; 3,93</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,93</t>
+          <t>0,59; 3,05</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,0</t>
+          <t>0,28; 2,16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,0</t>
+          <t>0,7; 2,05</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,79</t>
+          <t>0,75; 2,86</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,36</t>
+          <t>0,28; 1,37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,37</t>
+          <t>0,51; 2,28</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,66</t>
+          <t>1,17; 2,63</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,95</t>
+          <t>0,96; 2,73</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,42</t>
+          <t>0,72; 2,34</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,89</t>
+          <t>0,58; 1,97</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,09</t>
+          <t>1,08; 2,07</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,39</t>
+          <t>1,08; 2,43</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,67</t>
+          <t>0,65; 1,7</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ09_M-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_M-Provincia-trans_orig.xlsx
@@ -721,7 +721,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,35</t>
+          <t>0,64; 3,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,24</t>
+          <t>0,0; 1,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -741,12 +741,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,49</t>
+          <t>0,44; 5,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 4,78</t>
+          <t>0,45; 4,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,68</t>
+          <t>0,87; 3,78</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,83</t>
+          <t>0,6; 3,79</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,86</t>
+          <t>0,0; 1,95</t>
         </is>
       </c>
     </row>
@@ -861,12 +861,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,95</t>
+          <t>0,0; 2,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,43</t>
+          <t>0,0; 7,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,61</t>
+          <t>0,66; 3,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -891,27 +891,27 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 7,24</t>
+          <t>0,29; 6,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,56</t>
+          <t>0,47; 4,5</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,38</t>
+          <t>0,43; 2,27</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,21</t>
+          <t>0,68; 5,99</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 6,36</t>
+          <t>1,02; 5,97</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,16</t>
+          <t>0,0; 4,14</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,85</t>
+          <t>0,0; 3,0</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,0; 2,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 3,06</t>
+          <t>0,08; 2,93</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,04</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 4,64</t>
+          <t>0,37; 4,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 4,12</t>
+          <t>0,32; 4,15</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,26</t>
+          <t>0,38; 1,27</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,78</t>
+          <t>0,0; 3,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,56</t>
+          <t>0,63; 6,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,64</t>
+          <t>0,33; 2,53</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,56</t>
+          <t>0,63; 6,43</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,59</t>
+          <t>0,35; 3,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1571,47 +1571,47 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,82</t>
+          <t>0,0; 0,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,07</t>
+          <t>0,51; 5,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,1; 6,16</t>
+          <t>1,19; 5,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,0</t>
+          <t>0,07; 7,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,91</t>
+          <t>0,16; 1,86</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,07</t>
+          <t>0,51; 5,11</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,88</t>
+          <t>0,97; 3,67</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 5,5</t>
+          <t>0,58; 5,39</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,49</t>
+          <t>0,17; 1,43</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,72</t>
+          <t>0,0; 4,33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1711,47 +1711,47 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,64</t>
+          <t>0,29; 1,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,5</t>
+          <t>0,0; 2,47</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,65</t>
+          <t>0,93; 2,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,35</t>
+          <t>0,51; 4,35</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,98</t>
+          <t>0,0; 5,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,56</t>
+          <t>0,33; 2,56</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,1</t>
+          <t>0,68; 2,09</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,93</t>
+          <t>0,95; 3,86</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,05</t>
+          <t>0,65; 2,94</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,16</t>
+          <t>0,23; 1,94</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,05</t>
+          <t>0,76; 2,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,86</t>
+          <t>0,74; 2,8</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,37</t>
+          <t>0,28; 1,31</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,28</t>
+          <t>0,5; 2,28</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,63</t>
+          <t>1,15; 2,72</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,73</t>
+          <t>1,06; 2,87</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,34</t>
+          <t>0,81; 2,41</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,97</t>
+          <t>0,59; 1,89</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,07</t>
+          <t>1,1; 2,25</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,43</t>
+          <t>1,09; 2,39</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,7</t>
+          <t>0,67; 1,69</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ09_M-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_M-Provincia-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -653,37 +653,37 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>1,83</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,36</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1,59</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>1,76</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,92</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,17</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,83</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,36</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,66</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,5</t>
+          <t>0,84</t>
         </is>
       </c>
     </row>
@@ -721,37 +721,37 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,46</t>
+          <t>0,49; 6,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0,25; 4,78</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 4,0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,62; 3,49</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>0,0; 3,0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,17</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,44; 5,99</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,45; 4,78</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,0</t>
+          <t>0,0; 1,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,78</t>
+          <t>0,84; 3,57</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,79</t>
+          <t>0,62; 4,07</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,95</t>
+          <t>0,0; 2,52</t>
         </is>
       </c>
     </row>
@@ -788,49 +788,49 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,96</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,71</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,9</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2,76</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>1,06</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,48</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>3,3</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>3,0</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,96</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,71</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>1,9</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2,57</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1,9</t>
-        </is>
-      </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
           <t>1,11</t>
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,68</t>
+          <t>2,83</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0,97; 9,0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0,58; 3,37</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 6,0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0,38; 7,61</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>0,0; 3,71</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,36</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,89</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 9,0</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,36</t>
+          <t>0,0; 1,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,0</t>
+          <t>0,0; 7,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 6,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,5</t>
+          <t>0,5; 4,64</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,27</t>
+          <t>0,47; 2,37</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 5,99</t>
+          <t>0,69; 6,0</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,97</t>
+          <t>1,04; 6,35</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1,0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2,07</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,24</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>2,17</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,83</t>
         </is>
       </c>
     </row>
@@ -1001,39 +1001,39 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>0,0; 6,0</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>0,0; 6,0</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
           <t>0,0; 1,0</t>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,14</t>
+          <t>0,0; 4,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,0</t>
+          <t>0,0; 3,9</t>
         </is>
       </c>
     </row>
@@ -1073,37 +1073,37 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,96</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>2,54</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0,17</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,54</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,96</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,75</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,5</t>
         </is>
       </c>
     </row>
@@ -1141,37 +1141,37 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 4,51</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>0,0; 6,0</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,72</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,11</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,51</t>
+          <t>0,0; 0,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 2,93</t>
+          <t>0,09; 3,06</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,13</t>
+          <t>0,0; 1,62</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>1,96</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1223,47 +1223,47 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>0,83</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>1,0</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,96</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1,69</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0,81</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>1,69</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>0,85</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,56; 4,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,32; 1,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 4,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 4,15</t>
+          <t>0,32; 4,17</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,27</t>
+          <t>0,41; 1,29</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1358,34 +1358,34 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>0,72</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2,46</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
           <t>1,47</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,72</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2,72</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,72</t>
+          <t>2,46</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1426,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,75</t>
+          <t>0,0; 2,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,53; 6,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,94</t>
+          <t>0,0; 3,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,53</t>
+          <t>0,33; 2,56</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,43</t>
+          <t>0,53; 6,55</t>
         </is>
       </c>
     </row>
@@ -1488,49 +1488,49 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,11</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3,01</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3,26</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0,83</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1,55</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>2,0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,19</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0,18</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2,11</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,01</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,26</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0,84</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2,11</t>
-        </is>
-      </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
           <t>2,2</t>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>0,63</t>
         </is>
       </c>
     </row>
@@ -1556,52 +1556,52 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,51; 5,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,52</t>
+          <t>1,05; 6,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>0,97; 7,0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0,14; 1,84</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,46; 3,43</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
           <t>0,0; 4,0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,78</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0,51; 5,11</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1,19; 5,88</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0,07; 7,0</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,86</t>
+          <t>0,0; 0,72</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,11</t>
+          <t>0,51; 5,12</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,67</t>
+          <t>1,12; 3,87</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,43</t>
+          <t>0,19; 1,41</t>
         </is>
       </c>
     </row>
@@ -1628,42 +1628,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>0,91</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1,79</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2,0</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1,85</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>1,56</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>0,59</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>2,43</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>0,95</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0,91</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,79</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>2,0</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1,77</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>1,31</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0,0; 2,76</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0,93; 2,66</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0,52; 4,44</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 5,12</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>0,0; 4,33</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,15</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,18</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>0,46; 5,36</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>0,29; 1,6</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,47</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,93; 2,58</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,51; 4,35</t>
-        </is>
-      </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,03</t>
+          <t>0,38; 1,68</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,56</t>
+          <t>0,34; 2,46</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,09</t>
+          <t>0,7; 2,05</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,86</t>
+          <t>0,89; 3,81</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,94</t>
+          <t>0,58; 3,05</t>
         </is>
       </c>
     </row>
@@ -1768,42 +1768,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,17</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1,74</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1,8</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1,35</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>0,84</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1,27</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>1,52</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,74</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1,17</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1,74</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,8</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1,36</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>1,19</t>
         </is>
       </c>
     </row>
@@ -1836,42 +1836,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,94</t>
+          <t>0,51; 2,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,04</t>
+          <t>1,15; 2,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,8</t>
+          <t>1,11; 2,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,31</t>
+          <t>0,76; 2,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,28</t>
+          <t>0,28; 2,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,72</t>
+          <t>0,74; 2,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,87</t>
+          <t>0,73; 2,79</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,41</t>
+          <t>0,54; 1,61</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1881,17 +1881,17 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,25</t>
+          <t>1,1; 2,09</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,39</t>
+          <t>1,1; 2,39</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,69</t>
+          <t>0,8; 1,79</t>
         </is>
       </c>
     </row>
